--- a/employee_information_forms/030_personal_assistant_time_inout_form--employee_information_forms.xlsx
+++ b/employee_information_forms/030_personal_assistant_time_inout_form--employee_information_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>personalassistant_timein</t>
+          <t>personalassistant_timein_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time In</t>
+          <t>Personalassistant Timein 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>personalassistant_timeout</t>
+          <t>personalassistant_timeout_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time Out</t>
+          <t>Personalassistant Timeout 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>personalassistant_comments</t>
+          <t>personalassistant_comments_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Personalassistant Comments 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rendered Hours</t>
+          <t>Employee Renderedhours</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>personalassistant_comments</t>
+          <t>personalassistant_comments_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Personalassistant Comments 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Employee Note</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
